--- a/Data/EXCEL/Transfer/salemon/202206/6676-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6676-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C828605-5487-4578-BA8D-47623E64BC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F3C8B51-BDAC-452D-861A-79BFEEF1A1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6676-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,17 +1218,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="9.625" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="8" max="16" width="13.125" customWidth="1"/>
+    <col min="17" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1381,325 +1379,325 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>27.2</v>
+        <v>24.8</v>
       </c>
       <c r="C5" s="7">
-        <v>24.8</v>
+        <v>23.65</v>
       </c>
       <c r="D5" s="7">
-        <v>27.2</v>
+        <v>26.05</v>
       </c>
       <c r="E5" s="7">
-        <v>22.7</v>
+        <v>22.35</v>
       </c>
       <c r="F5" s="8">
-        <v>-2.4</v>
+        <v>-1.1499999999999999</v>
       </c>
       <c r="G5" s="8">
-        <v>-8.82</v>
+        <v>-4.6399999999999997</v>
       </c>
       <c r="H5" s="9">
-        <v>0.25800000000000001</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="I5" s="8">
-        <v>-35.200000000000003</v>
+        <v>-48.7</v>
       </c>
       <c r="J5" s="8">
-        <v>-24.3</v>
+        <v>-49.8</v>
       </c>
       <c r="K5" s="9">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="L5" s="10">
-        <v>47.8</v>
+        <v>26.8</v>
       </c>
       <c r="M5" s="9">
-        <v>0.25800000000000001</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="N5" s="8">
-        <v>-35.200000000000003</v>
+        <v>-48.7</v>
       </c>
       <c r="O5" s="8">
-        <v>-24.3</v>
+        <v>-49.8</v>
       </c>
       <c r="P5" s="9">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="Q5" s="10">
-        <v>47.8</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="C6" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="D6" s="7">
         <v>27.2</v>
       </c>
-      <c r="D6" s="7">
-        <v>32.200000000000003</v>
-      </c>
       <c r="E6" s="7">
-        <v>24.85</v>
-      </c>
-      <c r="F6" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="10">
-        <v>1.1200000000000001</v>
+        <v>22.7</v>
+      </c>
+      <c r="F6" s="8">
+        <v>-2.4</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-8.82</v>
       </c>
       <c r="H6" s="9">
-        <v>0.39800000000000002</v>
-      </c>
-      <c r="I6" s="10">
-        <v>24.3</v>
-      </c>
-      <c r="J6" s="10">
-        <v>61.1</v>
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="I6" s="8">
+        <v>-35.200000000000003</v>
+      </c>
+      <c r="J6" s="8">
+        <v>-24.3</v>
       </c>
       <c r="K6" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="L6" s="10">
-        <v>87.5</v>
+        <v>47.8</v>
       </c>
       <c r="M6" s="9">
-        <v>0.39800000000000002</v>
-      </c>
-      <c r="N6" s="10">
-        <v>24.3</v>
-      </c>
-      <c r="O6" s="10">
-        <v>61.1</v>
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="N6" s="8">
+        <v>-35.200000000000003</v>
+      </c>
+      <c r="O6" s="8">
+        <v>-24.3</v>
       </c>
       <c r="P6" s="9">
-        <v>1.1599999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="Q6" s="10">
-        <v>87.5</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>22.6</v>
+        <v>26.9</v>
       </c>
       <c r="C7" s="7">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="D7" s="7">
-        <v>30.35</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="E7" s="7">
-        <v>21.95</v>
+        <v>24.85</v>
       </c>
       <c r="F7" s="10">
-        <v>4.3</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="10">
-        <v>19.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="H7" s="9">
-        <v>0.32</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="I7" s="10">
-        <v>7.68</v>
+        <v>24.3</v>
       </c>
       <c r="J7" s="10">
-        <v>179.6</v>
+        <v>61.1</v>
       </c>
       <c r="K7" s="9">
-        <v>0.76500000000000001</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="L7" s="10">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="M7" s="9">
-        <v>0.32</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="N7" s="10">
-        <v>7.68</v>
+        <v>24.3</v>
       </c>
       <c r="O7" s="10">
-        <v>179.6</v>
+        <v>61.1</v>
       </c>
       <c r="P7" s="9">
-        <v>0.76500000000000001</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="Q7" s="10">
-        <v>105</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="C8" s="7">
-        <v>22.6</v>
+        <v>26.9</v>
       </c>
       <c r="D8" s="7">
-        <v>26.3</v>
+        <v>30.35</v>
       </c>
       <c r="E8" s="7">
-        <v>21.9</v>
-      </c>
-      <c r="F8" s="8">
-        <v>-0.4</v>
-      </c>
-      <c r="G8" s="8">
-        <v>-1.74</v>
+        <v>21.95</v>
+      </c>
+      <c r="F8" s="10">
+        <v>4.3</v>
+      </c>
+      <c r="G8" s="10">
+        <v>19.03</v>
       </c>
       <c r="H8" s="9">
-        <v>0.29799999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="I8" s="10">
-        <v>102.5</v>
+        <v>7.68</v>
       </c>
       <c r="J8" s="10">
-        <v>176</v>
+        <v>179.6</v>
       </c>
       <c r="K8" s="9">
-        <v>0.44500000000000001</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="L8" s="10">
-        <v>71.900000000000006</v>
+        <v>105</v>
       </c>
       <c r="M8" s="9">
-        <v>0.29799999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="N8" s="10">
-        <v>102.5</v>
+        <v>7.68</v>
       </c>
       <c r="O8" s="10">
-        <v>176</v>
+        <v>179.6</v>
       </c>
       <c r="P8" s="9">
-        <v>0.44500000000000001</v>
+        <v>0.76500000000000001</v>
       </c>
       <c r="Q8" s="10">
-        <v>71.900000000000006</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>23.55</v>
+        <v>23</v>
       </c>
       <c r="C9" s="7">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D9" s="7">
-        <v>36.299999999999997</v>
+        <v>26.3</v>
       </c>
       <c r="E9" s="7">
-        <v>20.05</v>
+        <v>21.9</v>
       </c>
       <c r="F9" s="8">
-        <v>-0.55000000000000004</v>
+        <v>-0.4</v>
       </c>
       <c r="G9" s="8">
-        <v>-2.34</v>
+        <v>-1.74</v>
       </c>
       <c r="H9" s="9">
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="I9" s="8">
-        <v>-31.4</v>
-      </c>
-      <c r="J9" s="8">
-        <v>-2.56</v>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="I9" s="10">
+        <v>102.5</v>
+      </c>
+      <c r="J9" s="10">
+        <v>176</v>
       </c>
       <c r="K9" s="9">
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="L9" s="8">
-        <v>-2.56</v>
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="L9" s="10">
+        <v>71.900000000000006</v>
       </c>
       <c r="M9" s="9">
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="N9" s="8">
-        <v>-31.4</v>
-      </c>
-      <c r="O9" s="8">
-        <v>-2.56</v>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="N9" s="10">
+        <v>102.5</v>
+      </c>
+      <c r="O9" s="10">
+        <v>176</v>
       </c>
       <c r="P9" s="9">
-        <v>0.14699999999999999</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>-2.56</v>
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>71.900000000000006</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>17</v>
+        <v>44562</v>
+      </c>
+      <c r="B10" s="7">
+        <v>23.55</v>
+      </c>
+      <c r="C10" s="7">
+        <v>23</v>
+      </c>
+      <c r="D10" s="7">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="E10" s="7">
+        <v>20.05</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-0.55000000000000004</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-2.34</v>
       </c>
       <c r="H10" s="9">
-        <v>0.214</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="I10" s="8">
-        <v>-23.6</v>
-      </c>
-      <c r="J10" s="10">
-        <v>596.4</v>
+        <v>-31.4</v>
+      </c>
+      <c r="J10" s="8">
+        <v>-2.56</v>
       </c>
       <c r="K10" s="9">
-        <v>2.41</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="L10" s="8">
-        <v>-42.6</v>
+        <v>-2.56</v>
       </c>
       <c r="M10" s="9">
-        <v>0.214</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="N10" s="8">
-        <v>-23.6</v>
-      </c>
-      <c r="O10" s="10">
-        <v>596.4</v>
+        <v>-31.4</v>
+      </c>
+      <c r="O10" s="8">
+        <v>-2.56</v>
       </c>
       <c r="P10" s="9">
-        <v>2.41</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="Q10" s="8">
-        <v>-42.6</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>17</v>
@@ -1720,39 +1718,39 @@
         <v>17</v>
       </c>
       <c r="H11" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="I11" s="10">
-        <v>103.1</v>
+        <v>0.214</v>
+      </c>
+      <c r="I11" s="8">
+        <v>-23.6</v>
       </c>
       <c r="J11" s="10">
-        <v>65</v>
+        <v>596.4</v>
       </c>
       <c r="K11" s="9">
-        <v>2.2000000000000002</v>
+        <v>2.41</v>
       </c>
       <c r="L11" s="8">
-        <v>-47.3</v>
+        <v>-42.6</v>
       </c>
       <c r="M11" s="9">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="N11" s="10">
-        <v>103.1</v>
+        <v>0.214</v>
+      </c>
+      <c r="N11" s="8">
+        <v>-23.6</v>
       </c>
       <c r="O11" s="10">
-        <v>65</v>
+        <v>596.4</v>
       </c>
       <c r="P11" s="9">
-        <v>2.2000000000000002</v>
+        <v>2.41</v>
       </c>
       <c r="Q11" s="8">
-        <v>-47.3</v>
+        <v>-42.6</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>17</v>
@@ -1773,39 +1771,39 @@
         <v>17</v>
       </c>
       <c r="H12" s="9">
-        <v>0.13800000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I12" s="10">
-        <v>30.7</v>
-      </c>
-      <c r="J12" s="8">
-        <v>-80.7</v>
+        <v>103.1</v>
+      </c>
+      <c r="J12" s="10">
+        <v>65</v>
       </c>
       <c r="K12" s="9">
-        <v>1.92</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="L12" s="8">
-        <v>-52.1</v>
+        <v>-47.3</v>
       </c>
       <c r="M12" s="9">
-        <v>0.13800000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="N12" s="10">
-        <v>30.7</v>
-      </c>
-      <c r="O12" s="8">
-        <v>-80.7</v>
+        <v>103.1</v>
+      </c>
+      <c r="O12" s="10">
+        <v>65</v>
       </c>
       <c r="P12" s="9">
-        <v>1.92</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q12" s="8">
-        <v>-52.1</v>
+        <v>-47.3</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1826,39 +1824,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>0.106</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-20.9</v>
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="I13" s="10">
+        <v>30.7</v>
       </c>
       <c r="J13" s="8">
-        <v>-65.3</v>
+        <v>-80.7</v>
       </c>
       <c r="K13" s="9">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="L13" s="8">
-        <v>-45.9</v>
+        <v>-52.1</v>
       </c>
       <c r="M13" s="9">
-        <v>0.106</v>
-      </c>
-      <c r="N13" s="8">
-        <v>-20.9</v>
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="N13" s="10">
+        <v>30.7</v>
       </c>
       <c r="O13" s="8">
-        <v>-65.3</v>
+        <v>-80.7</v>
       </c>
       <c r="P13" s="9">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" s="8">
-        <v>-45.9</v>
+        <v>-52.1</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1879,39 +1877,39 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
-        <v>0.13400000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="I14" s="8">
-        <v>-57.2</v>
+        <v>-20.9</v>
       </c>
       <c r="J14" s="8">
-        <v>-67</v>
+        <v>-65.3</v>
       </c>
       <c r="K14" s="9">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="L14" s="8">
-        <v>-43.9</v>
+        <v>-45.9</v>
       </c>
       <c r="M14" s="9">
-        <v>0.13400000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="N14" s="8">
-        <v>-57.2</v>
+        <v>-20.9</v>
       </c>
       <c r="O14" s="8">
-        <v>-67</v>
+        <v>-65.3</v>
       </c>
       <c r="P14" s="9">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" s="8">
-        <v>-43.9</v>
+        <v>-45.9</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>17</v>
@@ -1932,39 +1930,39 @@
         <v>17</v>
       </c>
       <c r="H15" s="9">
-        <v>0.312</v>
-      </c>
-      <c r="I15" s="10">
-        <v>18.3</v>
-      </c>
-      <c r="J15" s="10">
-        <v>15</v>
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="I15" s="8">
+        <v>-57.2</v>
+      </c>
+      <c r="J15" s="8">
+        <v>-67</v>
       </c>
       <c r="K15" s="9">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="L15" s="8">
-        <v>-40.200000000000003</v>
+        <v>-43.9</v>
       </c>
       <c r="M15" s="9">
-        <v>0.312</v>
-      </c>
-      <c r="N15" s="10">
-        <v>18.3</v>
-      </c>
-      <c r="O15" s="10">
-        <v>15</v>
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="N15" s="8">
+        <v>-57.2</v>
+      </c>
+      <c r="O15" s="8">
+        <v>-67</v>
       </c>
       <c r="P15" s="9">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="Q15" s="8">
-        <v>-40.200000000000003</v>
+        <v>-43.9</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>17</v>
@@ -1985,39 +1983,39 @@
         <v>17</v>
       </c>
       <c r="H16" s="9">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="I16" s="8">
-        <v>-22.6</v>
+        <v>0.312</v>
+      </c>
+      <c r="I16" s="10">
+        <v>18.3</v>
       </c>
       <c r="J16" s="10">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="K16" s="9">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="L16" s="8">
-        <v>-46.8</v>
+        <v>-40.200000000000003</v>
       </c>
       <c r="M16" s="9">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="N16" s="8">
-        <v>-22.6</v>
+        <v>0.312</v>
+      </c>
+      <c r="N16" s="10">
+        <v>18.3</v>
       </c>
       <c r="O16" s="10">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="P16" s="9">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="Q16" s="8">
-        <v>-46.8</v>
+        <v>-40.200000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>17</v>
@@ -2038,39 +2036,39 @@
         <v>17</v>
       </c>
       <c r="H17" s="9">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="I17" s="10">
-        <v>37.9</v>
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="I17" s="8">
+        <v>-22.6</v>
       </c>
       <c r="J17" s="10">
-        <v>2.58</v>
+        <v>101</v>
       </c>
       <c r="K17" s="9">
-        <v>0.96199999999999997</v>
+        <v>1.23</v>
       </c>
       <c r="L17" s="8">
-        <v>-55.7</v>
+        <v>-46.8</v>
       </c>
       <c r="M17" s="9">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="N17" s="10">
-        <v>37.9</v>
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="N17" s="8">
+        <v>-22.6</v>
       </c>
       <c r="O17" s="10">
-        <v>2.58</v>
+        <v>101</v>
       </c>
       <c r="P17" s="9">
-        <v>0.96199999999999997</v>
+        <v>1.23</v>
       </c>
       <c r="Q17" s="8">
-        <v>-55.7</v>
+        <v>-46.8</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2091,39 +2089,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="9">
-        <v>0.247</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="I18" s="10">
-        <v>115.7</v>
-      </c>
-      <c r="J18" s="8">
-        <v>-72.2</v>
+        <v>37.9</v>
+      </c>
+      <c r="J18" s="10">
+        <v>2.58</v>
       </c>
       <c r="K18" s="9">
-        <v>0.621</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="L18" s="8">
-        <v>-66.2</v>
+        <v>-55.7</v>
       </c>
       <c r="M18" s="9">
-        <v>0.247</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="N18" s="10">
-        <v>115.7</v>
-      </c>
-      <c r="O18" s="8">
-        <v>-72.2</v>
+        <v>37.9</v>
+      </c>
+      <c r="O18" s="10">
+        <v>2.58</v>
       </c>
       <c r="P18" s="9">
-        <v>0.621</v>
+        <v>0.96199999999999997</v>
       </c>
       <c r="Q18" s="8">
-        <v>-66.2</v>
+        <v>-55.7</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2144,39 +2142,39 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
-        <v>0.115</v>
+        <v>0.247</v>
       </c>
       <c r="I19" s="10">
-        <v>6.33</v>
+        <v>115.7</v>
       </c>
       <c r="J19" s="8">
-        <v>-62</v>
+        <v>-72.2</v>
       </c>
       <c r="K19" s="9">
-        <v>0.373</v>
+        <v>0.621</v>
       </c>
       <c r="L19" s="8">
-        <v>-60.7</v>
+        <v>-66.2</v>
       </c>
       <c r="M19" s="9">
-        <v>0.115</v>
+        <v>0.247</v>
       </c>
       <c r="N19" s="10">
-        <v>6.33</v>
+        <v>115.7</v>
       </c>
       <c r="O19" s="8">
-        <v>-62</v>
+        <v>-72.2</v>
       </c>
       <c r="P19" s="9">
-        <v>0.373</v>
+        <v>0.621</v>
       </c>
       <c r="Q19" s="8">
-        <v>-60.7</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>17</v>
@@ -2197,39 +2195,39 @@
         <v>17</v>
       </c>
       <c r="H20" s="9">
-        <v>0.108</v>
-      </c>
-      <c r="I20" s="8">
-        <v>-28.5</v>
+        <v>0.115</v>
+      </c>
+      <c r="I20" s="10">
+        <v>6.33</v>
       </c>
       <c r="J20" s="8">
-        <v>-69.099999999999994</v>
+        <v>-62</v>
       </c>
       <c r="K20" s="9">
-        <v>0.25900000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="L20" s="8">
-        <v>-60.1</v>
+        <v>-60.7</v>
       </c>
       <c r="M20" s="9">
-        <v>0.108</v>
-      </c>
-      <c r="N20" s="8">
-        <v>-28.5</v>
+        <v>0.115</v>
+      </c>
+      <c r="N20" s="10">
+        <v>6.33</v>
       </c>
       <c r="O20" s="8">
-        <v>-69.099999999999994</v>
+        <v>-62</v>
       </c>
       <c r="P20" s="9">
-        <v>0.25900000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="Q20" s="8">
-        <v>-60.1</v>
+        <v>-60.7</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>17</v>
@@ -2250,39 +2248,39 @@
         <v>17</v>
       </c>
       <c r="H21" s="9">
-        <v>0.151</v>
-      </c>
-      <c r="I21" s="10">
-        <v>390.2</v>
+        <v>0.108</v>
+      </c>
+      <c r="I21" s="8">
+        <v>-28.5</v>
       </c>
       <c r="J21" s="8">
-        <v>-49.6</v>
+        <v>-69.099999999999994</v>
       </c>
       <c r="K21" s="9">
-        <v>0.151</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="L21" s="8">
-        <v>-49.6</v>
+        <v>-60.1</v>
       </c>
       <c r="M21" s="9">
-        <v>0.151</v>
-      </c>
-      <c r="N21" s="10">
-        <v>390.2</v>
+        <v>0.108</v>
+      </c>
+      <c r="N21" s="8">
+        <v>-28.5</v>
       </c>
       <c r="O21" s="8">
-        <v>-49.6</v>
+        <v>-69.099999999999994</v>
       </c>
       <c r="P21" s="9">
-        <v>0.151</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="Q21" s="8">
-        <v>-49.6</v>
+        <v>-60.1</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>17</v>
@@ -2303,39 +2301,39 @@
         <v>17</v>
       </c>
       <c r="H22" s="9">
-        <v>3.0800000000000001E-2</v>
-      </c>
-      <c r="I22" s="8">
-        <v>-81.900000000000006</v>
+        <v>0.151</v>
+      </c>
+      <c r="I22" s="10">
+        <v>390.2</v>
       </c>
       <c r="J22" s="8">
-        <v>-70.400000000000006</v>
+        <v>-49.6</v>
       </c>
       <c r="K22" s="9">
-        <v>4.2</v>
-      </c>
-      <c r="L22" s="10">
-        <v>79.099999999999994</v>
+        <v>0.151</v>
+      </c>
+      <c r="L22" s="8">
+        <v>-49.6</v>
       </c>
       <c r="M22" s="9">
-        <v>3.0800000000000001E-2</v>
-      </c>
-      <c r="N22" s="8">
-        <v>-81.900000000000006</v>
+        <v>0.151</v>
+      </c>
+      <c r="N22" s="10">
+        <v>390.2</v>
       </c>
       <c r="O22" s="8">
-        <v>-70.400000000000006</v>
+        <v>-49.6</v>
       </c>
       <c r="P22" s="9">
-        <v>4.2</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>79.099999999999994</v>
+        <v>0.151</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>-49.6</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>17</v>
@@ -2356,39 +2354,39 @@
         <v>17</v>
       </c>
       <c r="H23" s="9">
-        <v>0.17</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="I23" s="8">
-        <v>-76.2</v>
+        <v>-81.900000000000006</v>
       </c>
       <c r="J23" s="8">
-        <v>-12.5</v>
+        <v>-70.400000000000006</v>
       </c>
       <c r="K23" s="9">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="L23" s="10">
-        <v>86</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="M23" s="9">
-        <v>0.17</v>
+        <v>3.0800000000000001E-2</v>
       </c>
       <c r="N23" s="8">
-        <v>-76.2</v>
+        <v>-81.900000000000006</v>
       </c>
       <c r="O23" s="8">
-        <v>-12.5</v>
+        <v>-70.400000000000006</v>
       </c>
       <c r="P23" s="9">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="Q23" s="10">
-        <v>86</v>
+        <v>79.099999999999994</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>17</v>
@@ -2409,39 +2407,39 @@
         <v>17</v>
       </c>
       <c r="H24" s="9">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="I24" s="10">
-        <v>135.1</v>
-      </c>
-      <c r="J24" s="10">
-        <v>163.5</v>
+        <v>0.17</v>
+      </c>
+      <c r="I24" s="8">
+        <v>-76.2</v>
+      </c>
+      <c r="J24" s="8">
+        <v>-12.5</v>
       </c>
       <c r="K24" s="9">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="L24" s="10">
-        <v>95.4</v>
+        <v>86</v>
       </c>
       <c r="M24" s="9">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="N24" s="10">
-        <v>135.1</v>
-      </c>
-      <c r="O24" s="10">
-        <v>163.5</v>
+        <v>0.17</v>
+      </c>
+      <c r="N24" s="8">
+        <v>-76.2</v>
+      </c>
+      <c r="O24" s="8">
+        <v>-12.5</v>
       </c>
       <c r="P24" s="9">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="Q24" s="10">
-        <v>95.4</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>17</v>
@@ -2462,39 +2460,39 @@
         <v>17</v>
       </c>
       <c r="H25" s="9">
-        <v>0.30399999999999999</v>
-      </c>
-      <c r="I25" s="8">
-        <v>-24.7</v>
-      </c>
-      <c r="J25" s="8">
-        <v>-3.77</v>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="I25" s="10">
+        <v>135.1</v>
+      </c>
+      <c r="J25" s="10">
+        <v>163.5</v>
       </c>
       <c r="K25" s="9">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="L25" s="10">
-        <v>85</v>
+        <v>95.4</v>
       </c>
       <c r="M25" s="9">
-        <v>0.30399999999999999</v>
-      </c>
-      <c r="N25" s="8">
-        <v>-24.7</v>
-      </c>
-      <c r="O25" s="8">
-        <v>-3.77</v>
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="N25" s="10">
+        <v>135.1</v>
+      </c>
+      <c r="O25" s="10">
+        <v>163.5</v>
       </c>
       <c r="P25" s="9">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="Q25" s="10">
-        <v>85</v>
+        <v>95.4</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>17</v>
@@ -2515,39 +2513,39 @@
         <v>17</v>
       </c>
       <c r="H26" s="9">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="I26" s="10">
-        <v>48.9</v>
-      </c>
-      <c r="J26" s="10">
-        <v>279.8</v>
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="I26" s="8">
+        <v>-24.7</v>
+      </c>
+      <c r="J26" s="8">
+        <v>-3.77</v>
       </c>
       <c r="K26" s="9">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="L26" s="10">
-        <v>104.2</v>
+        <v>85</v>
       </c>
       <c r="M26" s="9">
-        <v>0.40400000000000003</v>
-      </c>
-      <c r="N26" s="10">
-        <v>48.9</v>
-      </c>
-      <c r="O26" s="10">
-        <v>279.8</v>
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="N26" s="8">
+        <v>-24.7</v>
+      </c>
+      <c r="O26" s="8">
+        <v>-3.77</v>
       </c>
       <c r="P26" s="9">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="Q26" s="10">
-        <v>104.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>17</v>
@@ -2568,39 +2566,39 @@
         <v>17</v>
       </c>
       <c r="H27" s="9">
-        <v>0.27200000000000002</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="I27" s="10">
-        <v>106.7</v>
-      </c>
-      <c r="J27" s="8">
-        <v>-73.599999999999994</v>
+        <v>48.9</v>
+      </c>
+      <c r="J27" s="10">
+        <v>279.8</v>
       </c>
       <c r="K27" s="9">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="L27" s="10">
-        <v>90.4</v>
+        <v>104.2</v>
       </c>
       <c r="M27" s="9">
-        <v>0.27200000000000002</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="N27" s="10">
-        <v>106.7</v>
-      </c>
-      <c r="O27" s="8">
-        <v>-73.599999999999994</v>
+        <v>48.9</v>
+      </c>
+      <c r="O27" s="10">
+        <v>279.8</v>
       </c>
       <c r="P27" s="9">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="Q27" s="10">
-        <v>90.4</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>17</v>
@@ -2621,39 +2619,39 @@
         <v>17</v>
       </c>
       <c r="H28" s="9">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="I28" s="8">
-        <v>-60.5</v>
-      </c>
-      <c r="J28" s="10">
-        <v>16.600000000000001</v>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="I28" s="10">
+        <v>106.7</v>
+      </c>
+      <c r="J28" s="8">
+        <v>-73.599999999999994</v>
       </c>
       <c r="K28" s="9">
-        <v>2.2999999999999998</v>
+        <v>2.57</v>
       </c>
       <c r="L28" s="10">
-        <v>611.20000000000005</v>
+        <v>90.4</v>
       </c>
       <c r="M28" s="9">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="N28" s="8">
-        <v>-60.5</v>
-      </c>
-      <c r="O28" s="10">
-        <v>16.600000000000001</v>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="N28" s="10">
+        <v>106.7</v>
+      </c>
+      <c r="O28" s="8">
+        <v>-73.599999999999994</v>
       </c>
       <c r="P28" s="9">
-        <v>2.2999999999999998</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" s="10">
-        <v>611.20000000000005</v>
+        <v>90.4</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>17</v>
@@ -2674,39 +2672,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="9">
-        <v>0.33200000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="I29" s="8">
-        <v>-62.6</v>
+        <v>-60.5</v>
       </c>
       <c r="J29" s="10">
-        <v>87</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="K29" s="9">
-        <v>2.17</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="L29" s="10">
-        <v>928.8</v>
+        <v>611.20000000000005</v>
       </c>
       <c r="M29" s="9">
-        <v>0.33200000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="N29" s="8">
-        <v>-62.6</v>
+        <v>-60.5</v>
       </c>
       <c r="O29" s="10">
-        <v>87</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="P29" s="9">
-        <v>2.17</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="Q29" s="10">
-        <v>928.8</v>
+        <v>611.20000000000005</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>17</v>
@@ -2727,39 +2725,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="9">
-        <v>0.88900000000000001</v>
-      </c>
-      <c r="I30" s="10">
-        <v>194.8</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>17</v>
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="I30" s="8">
+        <v>-62.6</v>
+      </c>
+      <c r="J30" s="10">
+        <v>87</v>
       </c>
       <c r="K30" s="9">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="L30" s="10">
-        <v>5426.2</v>
+        <v>928.8</v>
       </c>
       <c r="M30" s="9">
-        <v>0.88900000000000001</v>
-      </c>
-      <c r="N30" s="10">
-        <v>194.8</v>
-      </c>
-      <c r="O30" s="9" t="s">
-        <v>17</v>
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="N30" s="8">
+        <v>-62.6</v>
+      </c>
+      <c r="O30" s="10">
+        <v>87</v>
       </c>
       <c r="P30" s="9">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="Q30" s="10">
-        <v>5426.2</v>
+        <v>928.8</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>17</v>
@@ -2780,39 +2778,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="9">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="I31" s="8">
-        <v>-13.7</v>
-      </c>
-      <c r="J31" s="10">
-        <v>805.9</v>
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="I31" s="10">
+        <v>194.8</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K31" s="9">
-        <v>0.95</v>
+        <v>1.84</v>
       </c>
       <c r="L31" s="10">
-        <v>2755.5</v>
+        <v>5426.2</v>
       </c>
       <c r="M31" s="9">
-        <v>0.30099999999999999</v>
-      </c>
-      <c r="N31" s="8">
-        <v>-13.7</v>
-      </c>
-      <c r="O31" s="10">
-        <v>805.9</v>
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="N31" s="10">
+        <v>194.8</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P31" s="9">
-        <v>0.95</v>
+        <v>1.84</v>
       </c>
       <c r="Q31" s="10">
-        <v>2755.5</v>
+        <v>5426.2</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>17</v>
@@ -2833,39 +2831,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="9">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="I32" s="10">
-        <v>16.7</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>17</v>
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="I32" s="8">
+        <v>-13.7</v>
+      </c>
+      <c r="J32" s="10">
+        <v>805.9</v>
       </c>
       <c r="K32" s="9">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>17</v>
+        <v>0.95</v>
+      </c>
+      <c r="L32" s="10">
+        <v>2755.5</v>
       </c>
       <c r="M32" s="9">
-        <v>0.34899999999999998</v>
-      </c>
-      <c r="N32" s="10">
-        <v>16.7</v>
-      </c>
-      <c r="O32" s="9" t="s">
-        <v>17</v>
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="N32" s="8">
+        <v>-13.7</v>
+      </c>
+      <c r="O32" s="10">
+        <v>805.9</v>
       </c>
       <c r="P32" s="9">
-        <v>0.64900000000000002</v>
-      </c>
-      <c r="Q32" s="9" t="s">
-        <v>17</v>
+        <v>0.95</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>2755.5</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>17</v>
@@ -2886,31 +2884,31 @@
         <v>17</v>
       </c>
       <c r="H33" s="9">
-        <v>0.29899999999999999</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="I33" s="10">
-        <v>187.8</v>
+        <v>16.7</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K33" s="9">
-        <v>0.29899999999999999</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="L33" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M33" s="9">
-        <v>0.29899999999999999</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="N33" s="10">
-        <v>187.8</v>
+        <v>16.7</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P33" s="9">
-        <v>0.29899999999999999</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="Q33" s="9" t="s">
         <v>17</v>
@@ -2918,7 +2916,7 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>17</v>
@@ -2939,39 +2937,39 @@
         <v>17</v>
       </c>
       <c r="H34" s="9">
-        <v>0.104</v>
-      </c>
-      <c r="I34" s="8">
-        <v>-46.5</v>
-      </c>
-      <c r="J34" s="8">
-        <v>-90.8</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="I34" s="10">
+        <v>187.8</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K34" s="9">
-        <v>2.34</v>
-      </c>
-      <c r="L34" s="10">
-        <v>64.2</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M34" s="9">
-        <v>0.104</v>
-      </c>
-      <c r="N34" s="8">
-        <v>-46.5</v>
-      </c>
-      <c r="O34" s="8">
-        <v>-90.8</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="N34" s="10">
+        <v>187.8</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P34" s="9">
-        <v>2.34</v>
-      </c>
-      <c r="Q34" s="10">
-        <v>64.2</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>17</v>
@@ -2992,39 +2990,39 @@
         <v>17</v>
       </c>
       <c r="H35" s="9">
-        <v>0.19400000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="I35" s="8">
-        <v>-28.5</v>
-      </c>
-      <c r="J35" s="10">
-        <v>181.4</v>
+        <v>-46.5</v>
+      </c>
+      <c r="J35" s="8">
+        <v>-90.8</v>
       </c>
       <c r="K35" s="9">
-        <v>2.2400000000000002</v>
+        <v>2.34</v>
       </c>
       <c r="L35" s="10">
-        <v>651.6</v>
+        <v>64.2</v>
       </c>
       <c r="M35" s="9">
-        <v>0.19400000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="N35" s="8">
-        <v>-28.5</v>
-      </c>
-      <c r="O35" s="10">
-        <v>181.4</v>
+        <v>-46.5</v>
+      </c>
+      <c r="O35" s="8">
+        <v>-90.8</v>
       </c>
       <c r="P35" s="9">
-        <v>2.2400000000000002</v>
+        <v>2.34</v>
       </c>
       <c r="Q35" s="10">
-        <v>651.6</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>17</v>
@@ -3045,39 +3043,39 @@
         <v>17</v>
       </c>
       <c r="H36" s="9">
-        <v>0.27200000000000002</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="I36" s="8">
-        <v>-14.1</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>17</v>
+        <v>-28.5</v>
+      </c>
+      <c r="J36" s="10">
+        <v>181.4</v>
       </c>
       <c r="K36" s="9">
-        <v>2.0499999999999998</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="L36" s="10">
-        <v>818.6</v>
+        <v>651.6</v>
       </c>
       <c r="M36" s="9">
-        <v>0.27200000000000002</v>
+        <v>0.19400000000000001</v>
       </c>
       <c r="N36" s="8">
-        <v>-14.1</v>
-      </c>
-      <c r="O36" s="9" t="s">
-        <v>17</v>
+        <v>-28.5</v>
+      </c>
+      <c r="O36" s="10">
+        <v>181.4</v>
       </c>
       <c r="P36" s="9">
-        <v>2.0499999999999998</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="Q36" s="10">
-        <v>818.6</v>
+        <v>651.6</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>17</v>
@@ -3098,39 +3096,39 @@
         <v>17</v>
       </c>
       <c r="H37" s="9">
-        <v>0.316</v>
-      </c>
-      <c r="I37" s="10">
-        <v>197.1</v>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="I37" s="8">
+        <v>-14.1</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K37" s="9">
-        <v>1.77</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="L37" s="10">
-        <v>696.7</v>
+        <v>818.6</v>
       </c>
       <c r="M37" s="9">
-        <v>0.316</v>
-      </c>
-      <c r="N37" s="10">
-        <v>197.1</v>
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="N37" s="8">
+        <v>-14.1</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P37" s="9">
-        <v>1.77</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="Q37" s="10">
-        <v>696.7</v>
+        <v>818.6</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>17</v>
@@ -3151,39 +3149,39 @@
         <v>17</v>
       </c>
       <c r="H38" s="9">
-        <v>0.106</v>
-      </c>
-      <c r="I38" s="8">
-        <v>-89.6</v>
+        <v>0.316</v>
+      </c>
+      <c r="I38" s="10">
+        <v>197.1</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K38" s="9">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="L38" s="10">
-        <v>554.6</v>
+        <v>696.7</v>
       </c>
       <c r="M38" s="9">
-        <v>0.106</v>
-      </c>
-      <c r="N38" s="8">
-        <v>-89.6</v>
+        <v>0.316</v>
+      </c>
+      <c r="N38" s="10">
+        <v>197.1</v>
       </c>
       <c r="O38" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P38" s="9">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" s="10">
-        <v>554.6</v>
+        <v>696.7</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>17</v>
@@ -3204,39 +3202,39 @@
         <v>17</v>
       </c>
       <c r="H39" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="I39" s="10">
-        <v>812.4</v>
+        <v>0.106</v>
+      </c>
+      <c r="I39" s="8">
+        <v>-89.6</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K39" s="9">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="L39" s="10">
-        <v>506.8</v>
+        <v>554.6</v>
       </c>
       <c r="M39" s="9">
-        <v>1.03</v>
-      </c>
-      <c r="N39" s="10">
-        <v>812.4</v>
+        <v>0.106</v>
+      </c>
+      <c r="N39" s="8">
+        <v>-89.6</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P39" s="9">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="Q39" s="10">
-        <v>506.8</v>
+        <v>554.6</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>17</v>
@@ -3257,39 +3255,39 @@
         <v>17</v>
       </c>
       <c r="H40" s="9">
-        <v>0.113</v>
-      </c>
-      <c r="I40" s="8">
-        <v>-36.6</v>
+        <v>1.03</v>
+      </c>
+      <c r="I40" s="10">
+        <v>812.4</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K40" s="9">
-        <v>0.32400000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="L40" s="10">
-        <v>45.3</v>
+        <v>506.8</v>
       </c>
       <c r="M40" s="9">
-        <v>0.113</v>
-      </c>
-      <c r="N40" s="8">
-        <v>-36.6</v>
+        <v>1.03</v>
+      </c>
+      <c r="N40" s="10">
+        <v>812.4</v>
       </c>
       <c r="O40" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P40" s="9">
-        <v>0.32400000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="Q40" s="10">
-        <v>45.3</v>
+        <v>506.8</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>17</v>
@@ -3310,39 +3308,39 @@
         <v>17</v>
       </c>
       <c r="H41" s="9">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>17</v>
+        <v>0.113</v>
+      </c>
+      <c r="I41" s="8">
+        <v>-36.6</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K41" s="9">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="L41" s="8">
-        <v>-5.28</v>
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="L41" s="10">
+        <v>45.3</v>
       </c>
       <c r="M41" s="9">
-        <v>0.17799999999999999</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>17</v>
+        <v>0.113</v>
+      </c>
+      <c r="N41" s="8">
+        <v>-36.6</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P41" s="9">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="Q41" s="8">
-        <v>-5.28</v>
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="Q41" s="10">
+        <v>45.3</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>17</v>
@@ -3363,39 +3361,39 @@
         <v>17</v>
       </c>
       <c r="H42" s="9">
-        <v>0</v>
-      </c>
-      <c r="I42" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J42" s="8">
-        <v>-100</v>
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K42" s="9">
-        <v>3.3300000000000003E-2</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="L42" s="8">
-        <v>-85.1</v>
+        <v>-5.28</v>
       </c>
       <c r="M42" s="9">
-        <v>0</v>
-      </c>
-      <c r="N42" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O42" s="8">
-        <v>-100</v>
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P42" s="9">
-        <v>3.3300000000000003E-2</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="Q42" s="8">
-        <v>-85.1</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>17</v>
@@ -3416,39 +3414,39 @@
         <v>17</v>
       </c>
       <c r="H43" s="9">
-        <v>3.3300000000000003E-2</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J43" s="8">
+        <v>-100</v>
       </c>
       <c r="K43" s="9">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="L43" s="9" t="s">
-        <v>17</v>
+      <c r="L43" s="8">
+        <v>-85.1</v>
       </c>
       <c r="M43" s="9">
-        <v>3.3300000000000003E-2</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N43" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O43" s="8">
+        <v>-100</v>
       </c>
       <c r="P43" s="9">
         <v>3.3300000000000003E-2</v>
       </c>
-      <c r="Q43" s="9" t="s">
-        <v>17</v>
+      <c r="Q43" s="8">
+        <v>-85.1</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>17</v>
@@ -3469,7 +3467,7 @@
         <v>17</v>
       </c>
       <c r="H44" s="9">
-        <v>0</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="I44" s="9" t="s">
         <v>17</v>
@@ -3478,13 +3476,13 @@
         <v>17</v>
       </c>
       <c r="K44" s="9">
-        <v>0</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="L44" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M44" s="9">
-        <v>0</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="N44" s="9" t="s">
         <v>17</v>
@@ -3493,7 +3491,7 @@
         <v>17</v>
       </c>
       <c r="P44" s="9">
-        <v>0</v>
+        <v>3.3300000000000003E-2</v>
       </c>
       <c r="Q44" s="9" t="s">
         <v>17</v>
@@ -3501,7 +3499,7 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>17</v>
@@ -3524,8 +3522,8 @@
       <c r="H45" s="9">
         <v>0</v>
       </c>
-      <c r="I45" s="8">
-        <v>-100</v>
+      <c r="I45" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>17</v>
@@ -3539,8 +3537,8 @@
       <c r="M45" s="9">
         <v>0</v>
       </c>
-      <c r="N45" s="8">
-        <v>-100</v>
+      <c r="N45" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>17</v>
@@ -3554,7 +3552,7 @@
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>17</v>
@@ -3575,39 +3573,39 @@
         <v>17</v>
       </c>
       <c r="H46" s="9">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="I46" s="10">
-        <v>1545.3</v>
-      </c>
-      <c r="J46" s="10">
-        <v>5226.3</v>
+        <v>0</v>
+      </c>
+      <c r="I46" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>1.43</v>
-      </c>
-      <c r="L46" s="10">
-        <v>544.4</v>
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M46" s="9">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="N46" s="10">
-        <v>1545.3</v>
-      </c>
-      <c r="O46" s="10">
-        <v>5226.3</v>
+        <v>0</v>
+      </c>
+      <c r="N46" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>1.43</v>
-      </c>
-      <c r="Q46" s="10">
-        <v>544.4</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>17</v>
@@ -3628,39 +3626,39 @@
         <v>17</v>
       </c>
       <c r="H47" s="9">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>17</v>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I47" s="10">
+        <v>1545.3</v>
+      </c>
+      <c r="J47" s="10">
+        <v>5226.3</v>
       </c>
       <c r="K47" s="9">
-        <v>0.29799999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="L47" s="10">
-        <v>48.9</v>
+        <v>544.4</v>
       </c>
       <c r="M47" s="9">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>17</v>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="N47" s="10">
+        <v>1545.3</v>
+      </c>
+      <c r="O47" s="10">
+        <v>5226.3</v>
       </c>
       <c r="P47" s="9">
-        <v>0.29799999999999999</v>
+        <v>1.43</v>
       </c>
       <c r="Q47" s="10">
-        <v>48.9</v>
+        <v>544.4</v>
       </c>
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>17</v>
@@ -3681,7 +3679,7 @@
         <v>17</v>
       </c>
       <c r="H48" s="9">
-        <v>0</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>17</v>
@@ -3690,13 +3688,13 @@
         <v>17</v>
       </c>
       <c r="K48" s="9">
-        <v>0.223</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="L48" s="10">
-        <v>11.2</v>
+        <v>48.9</v>
       </c>
       <c r="M48" s="9">
-        <v>0</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="N48" s="9" t="s">
         <v>17</v>
@@ -3705,15 +3703,15 @@
         <v>17</v>
       </c>
       <c r="P48" s="9">
-        <v>0.223</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="Q48" s="10">
-        <v>11.2</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>17</v>
@@ -3746,7 +3744,7 @@
         <v>0.223</v>
       </c>
       <c r="L49" s="10">
-        <v>51.1</v>
+        <v>11.2</v>
       </c>
       <c r="M49" s="9">
         <v>0</v>
@@ -3761,12 +3759,12 @@
         <v>0.223</v>
       </c>
       <c r="Q49" s="10">
-        <v>51.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>17</v>
@@ -3819,7 +3817,7 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>17</v>
@@ -3872,7 +3870,7 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3905,7 +3903,7 @@
         <v>0.223</v>
       </c>
       <c r="L52" s="10">
-        <v>139.30000000000001</v>
+        <v>51.1</v>
       </c>
       <c r="M52" s="9">
         <v>0</v>
@@ -3920,12 +3918,12 @@
         <v>0.223</v>
       </c>
       <c r="Q52" s="10">
-        <v>139.30000000000001</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3948,8 +3946,8 @@
       <c r="H53" s="9">
         <v>0</v>
       </c>
-      <c r="I53" s="8">
-        <v>-100</v>
+      <c r="I53" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>17</v>
@@ -3958,13 +3956,13 @@
         <v>0.223</v>
       </c>
       <c r="L53" s="10">
-        <v>310</v>
+        <v>139.30000000000001</v>
       </c>
       <c r="M53" s="9">
         <v>0</v>
       </c>
-      <c r="N53" s="8">
-        <v>-100</v>
+      <c r="N53" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>17</v>
@@ -3973,12 +3971,12 @@
         <v>0.223</v>
       </c>
       <c r="Q53" s="10">
-        <v>310</v>
+        <v>139.30000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -3999,10 +3997,10 @@
         <v>17</v>
       </c>
       <c r="H54" s="9">
-        <v>0.223</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I54" s="8">
+        <v>-100</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>17</v>
@@ -4014,10 +4012,10 @@
         <v>310</v>
       </c>
       <c r="M54" s="9">
-        <v>0.223</v>
-      </c>
-      <c r="N54" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N54" s="8">
+        <v>-100</v>
       </c>
       <c r="O54" s="9" t="s">
         <v>17</v>
@@ -4031,7 +4029,7 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4052,7 +4050,7 @@
         <v>17</v>
       </c>
       <c r="H55" s="9">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>17</v>
@@ -4061,13 +4059,13 @@
         <v>17</v>
       </c>
       <c r="K55" s="9">
-        <v>0</v>
-      </c>
-      <c r="L55" s="8">
-        <v>-100</v>
+        <v>0.223</v>
+      </c>
+      <c r="L55" s="10">
+        <v>310</v>
       </c>
       <c r="M55" s="9">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="N55" s="9" t="s">
         <v>17</v>
@@ -4076,15 +4074,15 @@
         <v>17</v>
       </c>
       <c r="P55" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="8">
-        <v>-100</v>
+        <v>0.223</v>
+      </c>
+      <c r="Q55" s="10">
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4110,8 +4108,8 @@
       <c r="I56" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J56" s="8">
-        <v>-100</v>
+      <c r="J56" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K56" s="9">
         <v>0</v>
@@ -4125,8 +4123,8 @@
       <c r="N56" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O56" s="8">
-        <v>-100</v>
+      <c r="O56" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P56" s="9">
         <v>0</v>
@@ -4137,7 +4135,7 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4190,54 +4188,107 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
+        <v>43101</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="9">
+        <v>0</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="8">
+        <v>-100</v>
+      </c>
+      <c r="K58" s="9">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
+        <v>-100</v>
+      </c>
+      <c r="M58" s="9">
+        <v>0</v>
+      </c>
+      <c r="N58" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O58" s="8">
+        <v>-100</v>
+      </c>
+      <c r="P58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
         <v>43070</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" s="9">
+      <c r="B59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="9">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="I58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" s="9">
+      <c r="I59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="9">
         <v>0.222</v>
       </c>
-      <c r="L58" s="8">
+      <c r="L59" s="8">
         <v>-19.5</v>
       </c>
-      <c r="M58" s="9">
+      <c r="M59" s="9">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="N58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P58" s="9">
+      <c r="N59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P59" s="9">
         <v>0.222</v>
       </c>
-      <c r="Q58" s="8">
+      <c r="Q59" s="8">
         <v>-19.5</v>
       </c>
     </row>
